--- a/src/ii_skills/shared/excel_templates/19_value_creation_waterfall.xlsx
+++ b/src/ii_skills/shared/excel_templates/19_value_creation_waterfall.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -39,14 +37,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0001395D"/>
         <bgColor rgb="0001395D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000A651"/>
-        <bgColor rgb="0000A651"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,22 +76,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -174,6 +160,411 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>MOIC Value Bridge ($M)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Value_Creation'!I3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Value_Creation'!$H$4:$H$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Value_Creation'!$I$4:$I$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Value_Creation'!J3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="00A651"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Value_Creation'!$H$4:$H$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Value_Creation'!$J$4:$J$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Value_Creation'!K3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Value_Creation'!$H$4:$H$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Value_Creation'!$K$4:$K$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Value_Creation'!L3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="01395D"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Value_Creation'!$H$4:$H$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Value_Creation'!$L$4:$L$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Value ($M)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>IRR Attribution Bridge (%)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Value_Creation'!I13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Value_Creation'!$H$14:$H$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Value_Creation'!$I$14:$I$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Value_Creation'!J13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="00A651"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Value_Creation'!$H$14:$H$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Value_Creation'!$J$14:$J$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Value_Creation'!K13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Value_Creation'!$H$14:$H$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Value_Creation'!$K$14:$K$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Value_Creation'!L13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="01395D"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Value_Creation'!$H$14:$H$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Value_Creation'!$L$14:$L$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>IRR (%)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -465,14 +856,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -482,346 +880,368 @@
           <t>VALUE CREATION ANALYSIS</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>MOIC Bridge Chart Data</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Base Case | 5-Year Hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Key Return Drivers | Base Case</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Increase</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Decrease</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Initial Investment</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>97</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Revenue Growth</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>97</v>
+      </c>
+      <c r="J5" t="n">
+        <v>173</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>MOIC VALUE BRIDGE</t>
-        </is>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Multiple Contraction</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>270</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Value ($M)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Cumulative ($M)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>% Contribution</t>
-        </is>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Debt Paydown</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>225</v>
+      </c>
+      <c r="J7" t="n">
+        <v>65</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Initial Equity Investment</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>97</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>97</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>(+) Revenue Growth</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>125</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>222</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Exit Value</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>(-) Multiple Contraction</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>-35</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>187</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>16%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>IRR Bridge Chart Data</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Increase</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Decrease</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>(-) Debt Paydown Effect</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>242</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Base (0%)</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Revenue Growth</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>35</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Exit Equity Value</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>310</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>310</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Multiple Contraction</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>35</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>14</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Series D Dilution</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>21</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Implied MOIC</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Net IRR</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
     <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>IRR VALUE BRIDGE</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Summary</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>IRR Impact</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Cumulative IRR</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>% Contribution</t>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Base (0% Return)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Entry Equity</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>$97M</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>(+) Revenue Growth</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>69%</t>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Exit Equity</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>$290M</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>(-) Multiple Contraction</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>13%</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>19%</t>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Implied MOIC</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3.0x</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>(+) Debt Paydown</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>12%</t>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Net IRR</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Net IRR</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Hold Period</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Target IRR (20%)</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>Met</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B6:E6"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>